--- a/examples/spreadsheets/example_fish.xlsx
+++ b/examples/spreadsheets/example_fish.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10209"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10118"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/brknight/Documents/GitHub/HandsFreeFishing/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/brknight/my_local_software/HandsFreeFishing/examples/spreadsheets/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{71652F1D-B5D3-0349-8205-8764E004E2C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{28FAC48C-DEFA-F546-AC58-D60F7A7A3D43}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="17820" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="17700" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,9 +25,6 @@
     <t>ViewerID</t>
   </si>
   <si>
-    <t>FIshID</t>
-  </si>
-  <si>
     <t>Species</t>
   </si>
   <si>
@@ -134,6 +131,9 @@
   </si>
   <si>
     <t>110524FishID15e</t>
+  </si>
+  <si>
+    <t>FishID</t>
   </si>
 </sst>
 </file>
@@ -413,33 +413,33 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>5</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>6</v>
       </c>
     </row>
     <row r="2" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A2" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D2" s="1"/>
       <c r="E2" s="1">
@@ -449,13 +449,13 @@
     </row>
     <row r="3" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A3" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D3" s="1"/>
       <c r="E3" s="1">
@@ -465,13 +465,13 @@
     </row>
     <row r="4" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A4" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B4" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="B4" s="1" t="s">
-        <v>12</v>
-      </c>
       <c r="C4" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D4" s="1"/>
       <c r="E4" s="1">
@@ -481,13 +481,13 @@
     </row>
     <row r="5" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A5" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B5" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="B5" s="1" t="s">
-        <v>14</v>
-      </c>
       <c r="C5" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E5" s="1">
         <v>1.25</v>
@@ -496,13 +496,13 @@
     </row>
     <row r="6" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A6" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B6" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="B6" s="1" t="s">
-        <v>16</v>
-      </c>
       <c r="C6" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E6" s="1">
         <v>1.36</v>
@@ -511,31 +511,31 @@
     </row>
     <row r="7" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A7" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E7" s="1">
         <v>1.68</v>
       </c>
       <c r="F7" s="1"/>
       <c r="G7" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A8" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B8" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="B8" s="1" t="s">
-        <v>21</v>
-      </c>
       <c r="C8" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E8" s="1">
         <v>1.2</v>
@@ -544,13 +544,13 @@
     </row>
     <row r="9" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A9" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B9" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="B9" s="1" t="s">
-        <v>23</v>
-      </c>
       <c r="C9" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E9" s="1">
         <v>1.1000000000000001</v>
@@ -559,13 +559,13 @@
     </row>
     <row r="10" spans="1:7" ht="13" x14ac:dyDescent="0.15">
       <c r="A10" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B10" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="B10" s="1" t="s">
-        <v>25</v>
-      </c>
       <c r="C10" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E10" s="1">
         <v>1.48</v>
@@ -574,13 +574,13 @@
     </row>
     <row r="11" spans="1:7" ht="13" x14ac:dyDescent="0.15">
       <c r="A11" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B11" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="B11" s="1" t="s">
-        <v>27</v>
-      </c>
       <c r="C11" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E11" s="1">
         <v>1</v>
@@ -589,13 +589,13 @@
     </row>
     <row r="12" spans="1:7" ht="13" x14ac:dyDescent="0.15">
       <c r="A12" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B12" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="B12" s="1" t="s">
-        <v>29</v>
-      </c>
       <c r="C12" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E12" s="1">
         <v>1.2</v>
@@ -604,13 +604,13 @@
     </row>
     <row r="13" spans="1:7" ht="13" x14ac:dyDescent="0.15">
       <c r="A13" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B13" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="B13" s="1" t="s">
-        <v>31</v>
-      </c>
       <c r="C13" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E13" s="1">
         <v>1.53</v>
@@ -619,13 +619,13 @@
     </row>
     <row r="14" spans="1:7" ht="13" x14ac:dyDescent="0.15">
       <c r="A14" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B14" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="B14" s="1" t="s">
-        <v>33</v>
-      </c>
       <c r="C14" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E14" s="1">
         <v>1.52</v>
@@ -634,13 +634,13 @@
     </row>
     <row r="15" spans="1:7" ht="13" x14ac:dyDescent="0.15">
       <c r="A15" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B15" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="B15" s="1" t="s">
-        <v>35</v>
-      </c>
       <c r="C15" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E15" s="1">
         <v>1.27</v>
@@ -649,13 +649,13 @@
     </row>
     <row r="16" spans="1:7" ht="13" x14ac:dyDescent="0.15">
       <c r="A16" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B16" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="B16" s="1" t="s">
-        <v>37</v>
-      </c>
       <c r="C16" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E16" s="1">
         <v>1.1599999999999999</v>
